--- a/data/trans_dic/P80_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P80_R-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,89</t>
+          <t>0,41; 1,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,48</t>
+          <t>0,05; 0,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,05</t>
+          <t>0,31; 1,17</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,19</t>
+          <t>0,96; 3,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,98</t>
+          <t>0,7; 1,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,74</t>
+          <t>0,97; 2,31</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,96</t>
+          <t>1,34; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,48</t>
+          <t>0,96; 2,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,97</t>
+          <t>1,41; 3,29</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,52</t>
+          <t>2,2; 4,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,26</t>
+          <t>1,6; 3,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,38</t>
+          <t>2,12; 3,63</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,56</t>
+          <t>1,72; 2,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,73</t>
+          <t>1,17; 1,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,98</t>
+          <t>1,52; 2,27</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5770</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6820</t>
+          <t>8749</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2252; 11994</t>
+          <t>2835; 13604</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>160; 3236</t>
+          <t>364; 5055</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3073; 13818</t>
+          <t>4419; 16616</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>19383</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>11445</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>25165</t>
+          <t>32184</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5636; 26125</t>
+          <t>10058; 33023</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6975; 18911</t>
+          <t>7507; 20275</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14593; 37351</t>
+          <t>20598; 48803</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>20407</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29956</t>
+          <t>34722</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8752; 34887</t>
+          <t>10730; 36328</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4700; 23083</t>
+          <t>7742; 24124</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17500; 48452</t>
+          <t>22630; 53064</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>32129</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24606</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52621</t>
+          <t>58542</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18387; 41868</t>
+          <t>21761; 46667</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15826; 35609</t>
+          <t>17892; 36626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>38685; 68249</t>
+          <t>44678; 76480</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44958; 88555</t>
+          <t>60769; 104966</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>36004; 63275</t>
+          <t>43517; 70790</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91253; 141103</t>
+          <t>110562; 164756</t>
         </is>
       </c>
     </row>
